--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260530_204327.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260530_204327.xlsx
@@ -6324,7 +6324,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260530_204327.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260530_204327.xlsx
@@ -6324,7 +6324,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
